--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T09:28:26+00:00</t>
+    <t>2025-02-06T11:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T11:21:55+00:00</t>
+    <t>2025-02-06T12:00:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T12:00:33+00:00</t>
+    <t>2025-02-10T09:34:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T09:34:03+00:00</t>
+    <t>2025-02-10T11:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:27:45+00:00</t>
+    <t>2025-02-12T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-LKFAbrechnungsGruppe-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-LKFAbrechnungsGruppe-valueset</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="901">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,6 +94,2556 @@
   </si>
   <si>
     <t>Concept</t>
+  </si>
+  <si>
+    <t>HDG01.01</t>
+  </si>
+  <si>
+    <t>Infektiöse Erkrankung des Gehirns/Rückenmarks und seiner Häute</t>
+  </si>
+  <si>
+    <t>HDG01.02</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien – Nervensystem</t>
+  </si>
+  <si>
+    <t>HDG01.03</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien und Abszesse – Nervensystem</t>
+  </si>
+  <si>
+    <t>HDG01.04</t>
+  </si>
+  <si>
+    <t>Zerebrale Degeneration/Kindheit</t>
+  </si>
+  <si>
+    <t>HDG01.05</t>
+  </si>
+  <si>
+    <t>Systematrophien und andere Degenerationen des Nervensystems</t>
+  </si>
+  <si>
+    <t>HDG01.06</t>
+  </si>
+  <si>
+    <t>Parkinson-Syndrom</t>
+  </si>
+  <si>
+    <t>HDG01.07</t>
+  </si>
+  <si>
+    <t>Andere extrapyramidale Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG01.08</t>
+  </si>
+  <si>
+    <t>Essentieller Tremor/Tick</t>
+  </si>
+  <si>
+    <t>HDG01.09</t>
+  </si>
+  <si>
+    <t>Hereditäre und idiopathische Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG01.10</t>
+  </si>
+  <si>
+    <t>Multiple Sklerose und andere demyelinisierende Erkrankungen des zentralen Nervensystems</t>
+  </si>
+  <si>
+    <t>HDG01.11</t>
+  </si>
+  <si>
+    <t>Zerebrale Kinderlähmung</t>
+  </si>
+  <si>
+    <t>HDG01.12</t>
+  </si>
+  <si>
+    <t>Epilepsie</t>
+  </si>
+  <si>
+    <t>HDG01.13</t>
+  </si>
+  <si>
+    <t>Primäre Kopfschmerzen</t>
+  </si>
+  <si>
+    <t>HDG01.14</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Hirnnerven</t>
+  </si>
+  <si>
+    <t>HDG01.15</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Spinalnerven/Nervenwurzeln</t>
+  </si>
+  <si>
+    <t>HDG01.16</t>
+  </si>
+  <si>
+    <t>Mononeuropathien</t>
+  </si>
+  <si>
+    <t>HDG01.17</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Nervengeflechte</t>
+  </si>
+  <si>
+    <t>HDG01.18</t>
+  </si>
+  <si>
+    <t>Polyneuropathien</t>
+  </si>
+  <si>
+    <t>HDG01.19</t>
+  </si>
+  <si>
+    <t>Myasthenie und akute Polyradikuloneuritis</t>
+  </si>
+  <si>
+    <t>HDG01.20</t>
+  </si>
+  <si>
+    <t>Subarachnoidalblutung</t>
+  </si>
+  <si>
+    <t>HDG01.21</t>
+  </si>
+  <si>
+    <t>Intrazerebrale Blutungen</t>
+  </si>
+  <si>
+    <t>HDG01.22</t>
+  </si>
+  <si>
+    <t>Ischämische zerebrale Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG01.23</t>
+  </si>
+  <si>
+    <t>Transiente ischämische Attacken</t>
+  </si>
+  <si>
+    <t>HDG01.24</t>
+  </si>
+  <si>
+    <t>Andere Hirngefäßerkrankungen und Spätfolgen</t>
+  </si>
+  <si>
+    <t>HDG01.25</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien - Nervensystem</t>
+  </si>
+  <si>
+    <t>HDG01.26</t>
+  </si>
+  <si>
+    <t>Schädelfrakturen</t>
+  </si>
+  <si>
+    <t>HDG01.27</t>
+  </si>
+  <si>
+    <t>Frakturen und Luxationen der Wirbelsäule mit/ohne Rückenmarksverletzungen</t>
+  </si>
+  <si>
+    <t>HDG01.28</t>
+  </si>
+  <si>
+    <t>Commotio cerebri</t>
+  </si>
+  <si>
+    <t>HDG01.29</t>
+  </si>
+  <si>
+    <t>Contusio cerebri</t>
+  </si>
+  <si>
+    <t>HDG01.30</t>
+  </si>
+  <si>
+    <t>Spätfolgen von Verletzungen des Nervensystems</t>
+  </si>
+  <si>
+    <t>HDG01.31</t>
+  </si>
+  <si>
+    <t>Sonstige Erkrankungen - Nervensystem</t>
+  </si>
+  <si>
+    <t>HDG01.32</t>
+  </si>
+  <si>
+    <t>Lokale und pseudoradikuläre Syndrome der Wirbelsäule</t>
+  </si>
+  <si>
+    <t>HDG01.33</t>
+  </si>
+  <si>
+    <t>Myelopathien unterschiedlicher Genese</t>
+  </si>
+  <si>
+    <t>HDG01.34</t>
+  </si>
+  <si>
+    <t>Chronische Schmerzsyndrome</t>
+  </si>
+  <si>
+    <t>HDG02.01</t>
+  </si>
+  <si>
+    <t>Infektionen im Nasen-/Rachenbereich</t>
+  </si>
+  <si>
+    <t>HDG02.02</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien - HNO</t>
+  </si>
+  <si>
+    <t>HDG02.03</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien - HNO</t>
+  </si>
+  <si>
+    <t>HDG02.04</t>
+  </si>
+  <si>
+    <t>Erkrankungen des Ohres/Mittelohres</t>
+  </si>
+  <si>
+    <t>HDG02.06</t>
+  </si>
+  <si>
+    <t>Komplizierte Mittelohraffektionen</t>
+  </si>
+  <si>
+    <t>HDG02.07</t>
+  </si>
+  <si>
+    <t>Otoneuropathien</t>
+  </si>
+  <si>
+    <t>HDG02.08</t>
+  </si>
+  <si>
+    <t>Sonstige Erkrankungen Nase, Nasennebenhöhlen, Rachen</t>
+  </si>
+  <si>
+    <t>HDG02.09</t>
+  </si>
+  <si>
+    <t>Akute Affektionen Nase, NNH, Rachen, obere Luftwege</t>
+  </si>
+  <si>
+    <t>HDG02.10</t>
+  </si>
+  <si>
+    <t>Chronische Affektionen der Nase</t>
+  </si>
+  <si>
+    <t>HDG02.11</t>
+  </si>
+  <si>
+    <t>Chronische Rachenaffektionen</t>
+  </si>
+  <si>
+    <t>HDG02.12</t>
+  </si>
+  <si>
+    <t>Chronische Affektionen des Larynx</t>
+  </si>
+  <si>
+    <t>HDG02.13</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien im HNO-Bereich</t>
+  </si>
+  <si>
+    <t>HDG02.14</t>
+  </si>
+  <si>
+    <t>Traumen im HNO-Bereich</t>
+  </si>
+  <si>
+    <t>HDG03.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien des Auges</t>
+  </si>
+  <si>
+    <t>HDG03.02</t>
+  </si>
+  <si>
+    <t>Operative Diagnosen am Auge</t>
+  </si>
+  <si>
+    <t>HDG03.03</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen I</t>
+  </si>
+  <si>
+    <t>HDG03.04</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen II</t>
+  </si>
+  <si>
+    <t>HDG03.05</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen III</t>
+  </si>
+  <si>
+    <t>HDG03.06</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen IV</t>
+  </si>
+  <si>
+    <t>HDG03.07</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen V</t>
+  </si>
+  <si>
+    <t>HDG03.08</t>
+  </si>
+  <si>
+    <t>Augen-Diagnosen VI</t>
+  </si>
+  <si>
+    <t>HDG04.01</t>
+  </si>
+  <si>
+    <t>Akute Affektionen der Mundhöhle</t>
+  </si>
+  <si>
+    <t>HDG04.02</t>
+  </si>
+  <si>
+    <t>Sonstige Erkrankungen Zähne/Zahnhalteapparat/Mundhöhle</t>
+  </si>
+  <si>
+    <t>HDG04.03</t>
+  </si>
+  <si>
+    <t>Krankheiten der Kiefer</t>
+  </si>
+  <si>
+    <t>HDG04.04</t>
+  </si>
+  <si>
+    <t>Dentofaziale Anomalien</t>
+  </si>
+  <si>
+    <t>HDG04.05</t>
+  </si>
+  <si>
+    <t>Frakturen der Gesichtsknochen</t>
+  </si>
+  <si>
+    <t>HDG05.01</t>
+  </si>
+  <si>
+    <t>Tuberkulose</t>
+  </si>
+  <si>
+    <t>HDG05.02</t>
+  </si>
+  <si>
+    <t>Akute Affektionen der mittleren Atemwege und Atelektase</t>
+  </si>
+  <si>
+    <t>HDG05.03</t>
+  </si>
+  <si>
+    <t>Pneumonie und Bronchiolitis</t>
+  </si>
+  <si>
+    <t>HDG05.04</t>
+  </si>
+  <si>
+    <t>Chronische Bronchialerkrankungen und Emphysem</t>
+  </si>
+  <si>
+    <t>HDG05.05</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der unteren Atmungsorgane</t>
+  </si>
+  <si>
+    <t>HDG05.06</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der unteren Atmungsorgane</t>
+  </si>
+  <si>
+    <t>HDG05.07</t>
+  </si>
+  <si>
+    <t>Diffuse Lungenparenchymerkrankungen</t>
+  </si>
+  <si>
+    <t>HDG05.08</t>
+  </si>
+  <si>
+    <t>Erkrankungen des Pleuraraumes</t>
+  </si>
+  <si>
+    <t>HDG05.09</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien der Atmungsorgane</t>
+  </si>
+  <si>
+    <t>HDG05.10</t>
+  </si>
+  <si>
+    <t>Larynx- Thoraxverletzungen außer Herz</t>
+  </si>
+  <si>
+    <t>HDG05.11</t>
+  </si>
+  <si>
+    <t>Affektionen der Atmungsorgane</t>
+  </si>
+  <si>
+    <t>HDG06.02</t>
+  </si>
+  <si>
+    <t>Hypertonie</t>
+  </si>
+  <si>
+    <t>HDG06.03</t>
+  </si>
+  <si>
+    <t>Linksherzinsuffizienz und akute Herzerkrankungen</t>
+  </si>
+  <si>
+    <t>HDG06.04</t>
+  </si>
+  <si>
+    <t>Chronische Herzerkrankungen</t>
+  </si>
+  <si>
+    <t>HDG06.05</t>
+  </si>
+  <si>
+    <t>Akute entzündliche Herzkrankheiten</t>
+  </si>
+  <si>
+    <t>HDG06.06</t>
+  </si>
+  <si>
+    <t>Herzklappenfehler und Kardiomyopathie</t>
+  </si>
+  <si>
+    <t>HDG06.07</t>
+  </si>
+  <si>
+    <t>Komplizierte Herzrhythmusstörungen</t>
+  </si>
+  <si>
+    <t>HDG06.08</t>
+  </si>
+  <si>
+    <t>Herzrhythmusstörungen</t>
+  </si>
+  <si>
+    <t>HDG06.09</t>
+  </si>
+  <si>
+    <t>Aortenaneurysmen, andere Affektionen der Aorta</t>
+  </si>
+  <si>
+    <t>HDG06.10</t>
+  </si>
+  <si>
+    <t>Symptome und Zustände betreffend Herz und Kreislauf</t>
+  </si>
+  <si>
+    <t>HDG06.11</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien des Herzens und der großen Gefäße</t>
+  </si>
+  <si>
+    <t>HDG07.01</t>
+  </si>
+  <si>
+    <t>Nichtentzündliche Affektionen der Arterien, außer Aorta</t>
+  </si>
+  <si>
+    <t>HDG07.02</t>
+  </si>
+  <si>
+    <t>Entzündliche Affektionen der Arterien</t>
+  </si>
+  <si>
+    <t>HDG07.04</t>
+  </si>
+  <si>
+    <t>Affektionen der Venen</t>
+  </si>
+  <si>
+    <t>HDG07.05</t>
+  </si>
+  <si>
+    <t>Komplizierte Affektionen der Venen</t>
+  </si>
+  <si>
+    <t>HDG07.06</t>
+  </si>
+  <si>
+    <t>Verletzung der peripheren Blutgefäße</t>
+  </si>
+  <si>
+    <t>HDG07.07</t>
+  </si>
+  <si>
+    <t>Affektionen des Lymphsystems</t>
+  </si>
+  <si>
+    <t>HDG08.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien des Gastrointestinums</t>
+  </si>
+  <si>
+    <t>HDG08.02</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien Leber, Galle, Pankreas</t>
+  </si>
+  <si>
+    <t>HDG08.03</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien des Gastrointestinaltrakts</t>
+  </si>
+  <si>
+    <t>HDG08.04</t>
+  </si>
+  <si>
+    <t>Einfache Affektionen Ösophagus, Magen, Duodenum</t>
+  </si>
+  <si>
+    <t>HDG08.05</t>
+  </si>
+  <si>
+    <t>Komplizierte Affektionen Ösophagus, Magen, Duodenum</t>
+  </si>
+  <si>
+    <t>HDG08.06</t>
+  </si>
+  <si>
+    <t>Appendicitis und Darmdivertikel</t>
+  </si>
+  <si>
+    <t>HDG08.07</t>
+  </si>
+  <si>
+    <t>Komplizierte abdominale Hernien</t>
+  </si>
+  <si>
+    <t>HDG08.08</t>
+  </si>
+  <si>
+    <t>Chronisch entzündliche Darmerkrankung</t>
+  </si>
+  <si>
+    <t>HDG08.09</t>
+  </si>
+  <si>
+    <t>Malabsorption</t>
+  </si>
+  <si>
+    <t>HDG08.10</t>
+  </si>
+  <si>
+    <t>Komplizierte Darmerkrankungen</t>
+  </si>
+  <si>
+    <t>HDG08.11</t>
+  </si>
+  <si>
+    <t>Sonstige Magen-Darm Affektionen</t>
+  </si>
+  <si>
+    <t>HDG08.12</t>
+  </si>
+  <si>
+    <t>Komplizierte anorektale Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG08.13</t>
+  </si>
+  <si>
+    <t>Andere anorektale Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG08.14</t>
+  </si>
+  <si>
+    <t>Akute Hepatitis</t>
+  </si>
+  <si>
+    <t>HDG08.15</t>
+  </si>
+  <si>
+    <t>Erkrankungen von Leber, Galle, Pankreas</t>
+  </si>
+  <si>
+    <t>HDG08.16</t>
+  </si>
+  <si>
+    <t>Komplizierte Erkrankungen von Leber, Galle, Pankreas</t>
+  </si>
+  <si>
+    <t>HDG08.17</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien des Verdauungstraktes</t>
+  </si>
+  <si>
+    <t>HDG08.18</t>
+  </si>
+  <si>
+    <t>Symptome und Zustände betreffend Verdauungssystem</t>
+  </si>
+  <si>
+    <t>HDG08.19</t>
+  </si>
+  <si>
+    <t>Verletzung intraabdominaler Organe und Blutgefäße</t>
+  </si>
+  <si>
+    <t>HDG09.01</t>
+  </si>
+  <si>
+    <t>Andere Infektionen der Urogenitalorgane</t>
+  </si>
+  <si>
+    <t>HDG09.02</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der Harnblase, Niere, anderer Harnorgane</t>
+  </si>
+  <si>
+    <t>HDG09.03</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der Niere und anderer Harnorgane</t>
+  </si>
+  <si>
+    <t>HDG09.04</t>
+  </si>
+  <si>
+    <t>Nephropathie</t>
+  </si>
+  <si>
+    <t>HDG09.05</t>
+  </si>
+  <si>
+    <t>Urethralsyndrom</t>
+  </si>
+  <si>
+    <t>HDG09.06</t>
+  </si>
+  <si>
+    <t>Nephropathie mit schweren systemischen Komplikationen</t>
+  </si>
+  <si>
+    <t>HDG09.07</t>
+  </si>
+  <si>
+    <t>Nephrolithiasis</t>
+  </si>
+  <si>
+    <t>HDG09.08</t>
+  </si>
+  <si>
+    <t>Affektionen der ableitenden Harnwege</t>
+  </si>
+  <si>
+    <t>HDG09.09</t>
+  </si>
+  <si>
+    <t>Verletzungen der Beckenorgane und Niere</t>
+  </si>
+  <si>
+    <t>HDG10.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der Prostata, Hoden, Penis, andere</t>
+  </si>
+  <si>
+    <t>HDG10.02</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG10.03</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Prostata und der äußeren Genitale</t>
+  </si>
+  <si>
+    <t>HDG10.04</t>
+  </si>
+  <si>
+    <t>Affektionen der äußeren Genitale</t>
+  </si>
+  <si>
+    <t>HDG10.05</t>
+  </si>
+  <si>
+    <t>Verletzungen der Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.02</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.03</t>
+  </si>
+  <si>
+    <t>Akute entzündliche Erkrankungen der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.04</t>
+  </si>
+  <si>
+    <t>Chronische entzündliche Erkrankungen der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.05</t>
+  </si>
+  <si>
+    <t>Lageanomalien des Uterus</t>
+  </si>
+  <si>
+    <t>HDG11.06</t>
+  </si>
+  <si>
+    <t>Nichtentzündliche Affektionen der Adnexe</t>
+  </si>
+  <si>
+    <t>HDG11.07</t>
+  </si>
+  <si>
+    <t>Funktionelle Störungen der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.08</t>
+  </si>
+  <si>
+    <t>Nichtentzündliche Affektionen des Uterus, Vagina, Vulva inklusive Dysplasien</t>
+  </si>
+  <si>
+    <t>HDG11.09</t>
+  </si>
+  <si>
+    <t>Sonstige Erkrankungen der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG11.10</t>
+  </si>
+  <si>
+    <t>Kongenitale Anomalien der weiblichen Genitalorgane</t>
+  </si>
+  <si>
+    <t>HDG12.01</t>
+  </si>
+  <si>
+    <t>Abortus</t>
+  </si>
+  <si>
+    <t>HDG12.03</t>
+  </si>
+  <si>
+    <t>Blutung in der Spätschwangerschaft</t>
+  </si>
+  <si>
+    <t>HDG12.04</t>
+  </si>
+  <si>
+    <t>Komplikationen in der Schwangerschaft und im Wochenbett</t>
+  </si>
+  <si>
+    <t>HDG12.07</t>
+  </si>
+  <si>
+    <t>Peri-/postpartale Komplikationen</t>
+  </si>
+  <si>
+    <t>HDG13.01</t>
+  </si>
+  <si>
+    <t>Schwere fetale Schädigungen</t>
+  </si>
+  <si>
+    <t>HDG13.02</t>
+  </si>
+  <si>
+    <t>Leichte fetale Schädigungen</t>
+  </si>
+  <si>
+    <t>HDG14.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien von Knochen, Bindegewebe und Weichteilen</t>
+  </si>
+  <si>
+    <t>HDG14.02</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien von Knochen, Bindegewebe und Weichteilen</t>
+  </si>
+  <si>
+    <t>HDG14.03</t>
+  </si>
+  <si>
+    <t>Osteomyelitis und akute Arthritis</t>
+  </si>
+  <si>
+    <t>HDG14.04</t>
+  </si>
+  <si>
+    <t>Chronisch entzündliche und degenerative Erkrankungen am Bewegungsapparat</t>
+  </si>
+  <si>
+    <t>HDG14.05</t>
+  </si>
+  <si>
+    <t>Affektionen der Weichteile am Bewegungsapparat</t>
+  </si>
+  <si>
+    <t>HDG14.06</t>
+  </si>
+  <si>
+    <t>Anomalien und Deformitäten des Bewegungsapparates</t>
+  </si>
+  <si>
+    <t>HDG14.07</t>
+  </si>
+  <si>
+    <t>Andere Affektionen am Bewegungsapparat</t>
+  </si>
+  <si>
+    <t>HDG14.08</t>
+  </si>
+  <si>
+    <t>Spätfolgen von Verletzungen von Muskeln, Skelett, Bindegewebe, Haut</t>
+  </si>
+  <si>
+    <t>HDG15.01</t>
+  </si>
+  <si>
+    <t>Frakturen der oberen Extremität, außer Hand</t>
+  </si>
+  <si>
+    <t>HDG15.02</t>
+  </si>
+  <si>
+    <t>Frakturen Hand/Vorfuß</t>
+  </si>
+  <si>
+    <t>HDG15.03</t>
+  </si>
+  <si>
+    <t>Frakturen der unteren Extremität/Becken, außer Vorfuß</t>
+  </si>
+  <si>
+    <t>HDG15.04</t>
+  </si>
+  <si>
+    <t>Luxationen, Distorsionen, Kontusionen, Quetschungen</t>
+  </si>
+  <si>
+    <t>HDG15.05</t>
+  </si>
+  <si>
+    <t>Kniegelenkschädigungen</t>
+  </si>
+  <si>
+    <t>HDG15.06</t>
+  </si>
+  <si>
+    <t>Hautverletzungen, Verbrennungen Grad I-II</t>
+  </si>
+  <si>
+    <t>HDG15.07</t>
+  </si>
+  <si>
+    <t>Verbrennungen großflächig, Grad III-IV</t>
+  </si>
+  <si>
+    <t>HDG15.08</t>
+  </si>
+  <si>
+    <t>Traumatische Amputationen</t>
+  </si>
+  <si>
+    <t>HDG16.01</t>
+  </si>
+  <si>
+    <t>Komplizierte Infektionen des Verdauungstraktes</t>
+  </si>
+  <si>
+    <t>HDG16.02</t>
+  </si>
+  <si>
+    <t>Andere Infektionen des Verdauungstraktes</t>
+  </si>
+  <si>
+    <t>HDG16.03</t>
+  </si>
+  <si>
+    <t>Bakterielle Zoonosen</t>
+  </si>
+  <si>
+    <t>HDG16.04</t>
+  </si>
+  <si>
+    <t>Andere bakterielle Krankheiten</t>
+  </si>
+  <si>
+    <t>HDG16.05</t>
+  </si>
+  <si>
+    <t>Komplizierte bakterielle Infektionen, Sepsis</t>
+  </si>
+  <si>
+    <t>HDG16.06</t>
+  </si>
+  <si>
+    <t>Virusinfektionen</t>
+  </si>
+  <si>
+    <t>HDG16.07</t>
+  </si>
+  <si>
+    <t>Nichtheimische Infektionen durch Protozoen</t>
+  </si>
+  <si>
+    <t>HDG16.08</t>
+  </si>
+  <si>
+    <t>Mykosen</t>
+  </si>
+  <si>
+    <t>HDG16.09</t>
+  </si>
+  <si>
+    <t>Andere infektiöse und parasitäre Krankheiten</t>
+  </si>
+  <si>
+    <t>HDG16.10</t>
+  </si>
+  <si>
+    <t>Helminthosen</t>
+  </si>
+  <si>
+    <t>HDG16.11</t>
+  </si>
+  <si>
+    <t>Befunde und Zustände betreffend Infektionen</t>
+  </si>
+  <si>
+    <t>HDG16.12</t>
+  </si>
+  <si>
+    <t>AIDS-Erkrankung</t>
+  </si>
+  <si>
+    <t>HDG16.13</t>
+  </si>
+  <si>
+    <t>HIV-Infektion und assoziierte Erkrankungen</t>
+  </si>
+  <si>
+    <t>HDG17.01</t>
+  </si>
+  <si>
+    <t>Akute Leukämie</t>
+  </si>
+  <si>
+    <t>HDG17.02</t>
+  </si>
+  <si>
+    <t>Hochmaligne Non-Hodgkin Lymphome</t>
+  </si>
+  <si>
+    <t>HDG17.03</t>
+  </si>
+  <si>
+    <t>Morbus Hodgkin</t>
+  </si>
+  <si>
+    <t>HDG17.04</t>
+  </si>
+  <si>
+    <t>Andere hämatologische Neoplasien</t>
+  </si>
+  <si>
+    <t>HDG17.05</t>
+  </si>
+  <si>
+    <t>Mangelanämien</t>
+  </si>
+  <si>
+    <t>HDG17.06</t>
+  </si>
+  <si>
+    <t>Andere Erkrankungen des Blutes</t>
+  </si>
+  <si>
+    <t>HDG17.07</t>
+  </si>
+  <si>
+    <t>Aplastische Anämien</t>
+  </si>
+  <si>
+    <t>HDG17.08</t>
+  </si>
+  <si>
+    <t>Koagulopathien</t>
+  </si>
+  <si>
+    <t>HDG18.01</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien anderer endokriner Drüsen</t>
+  </si>
+  <si>
+    <t>HDG18.02</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien anderer endokriner Drüsen</t>
+  </si>
+  <si>
+    <t>HDG18.03</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Schilddrüse und Nebenschilddrüse</t>
+  </si>
+  <si>
+    <t>HDG18.04</t>
+  </si>
+  <si>
+    <t>Diabetisches Koma u. komplizierte Stoffwechselstörungen</t>
+  </si>
+  <si>
+    <t>HDG18.05</t>
+  </si>
+  <si>
+    <t>Erkrankungen der Bauchspeicheldrüse</t>
+  </si>
+  <si>
+    <t>HDG18.06</t>
+  </si>
+  <si>
+    <t>Sekretionsstörungen der Hypophyse und Nebenniere</t>
+  </si>
+  <si>
+    <t>HDG18.07</t>
+  </si>
+  <si>
+    <t>Funktionsstörungen der Gonaden</t>
+  </si>
+  <si>
+    <t>HDG18.08</t>
+  </si>
+  <si>
+    <t>Andere endokrine Störungen</t>
+  </si>
+  <si>
+    <t>HDG18.09</t>
+  </si>
+  <si>
+    <t>Mangelerkrankungen und Störungen des Flüssigkeitshaushaltes</t>
+  </si>
+  <si>
+    <t>HDG18.10</t>
+  </si>
+  <si>
+    <t>Stoffwechselstörungen</t>
+  </si>
+  <si>
+    <t>HDG19.03</t>
+  </si>
+  <si>
+    <t>Andere Erkrankungen der Mamma</t>
+  </si>
+  <si>
+    <t>HDG19.04</t>
+  </si>
+  <si>
+    <t>Virale Infektionen der Haut</t>
+  </si>
+  <si>
+    <t>HDG19.05</t>
+  </si>
+  <si>
+    <t>Geschlechtskrankheiten</t>
+  </si>
+  <si>
+    <t>HDG19.06</t>
+  </si>
+  <si>
+    <t>Einfache Mykosen</t>
+  </si>
+  <si>
+    <t>HDG19.07</t>
+  </si>
+  <si>
+    <t>Komplizierte Affektionen der Haut</t>
+  </si>
+  <si>
+    <t>HDG19.08</t>
+  </si>
+  <si>
+    <t>Einfache Affektionen der Haut</t>
+  </si>
+  <si>
+    <t>HDG19.09</t>
+  </si>
+  <si>
+    <t>Kollagenosen und Sarkoidose</t>
+  </si>
+  <si>
+    <t>HDG19.10</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der Haut</t>
+  </si>
+  <si>
+    <t>HDG19.11</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der Haut</t>
+  </si>
+  <si>
+    <t>HDG19.12</t>
+  </si>
+  <si>
+    <t>Maligne Neoplasien der Mamma</t>
+  </si>
+  <si>
+    <t>HDG19.13</t>
+  </si>
+  <si>
+    <t>Benigne Neoplasien der Mamma</t>
+  </si>
+  <si>
+    <t>HDG20.01</t>
+  </si>
+  <si>
+    <t>Alzheimersche Krankheit und nicht-vaskuläre Demenzen</t>
+  </si>
+  <si>
+    <t>HDG20.02</t>
+  </si>
+  <si>
+    <t>Demenzen mit psychiatrischen Syndromen</t>
+  </si>
+  <si>
+    <t>HDG20.03</t>
+  </si>
+  <si>
+    <t>Vaskuläre Demenz</t>
+  </si>
+  <si>
+    <t>HDG20.04</t>
+  </si>
+  <si>
+    <t>Alkoholentzugssyndrom und -psychosen</t>
+  </si>
+  <si>
+    <t>HDG20.06</t>
+  </si>
+  <si>
+    <t>Drogenentzugssyndrome und -psychosen</t>
+  </si>
+  <si>
+    <t>HDG20.08</t>
+  </si>
+  <si>
+    <t>Akute exogene Reaktionstypen/ Psychogene Reaktion</t>
+  </si>
+  <si>
+    <t>HDG20.09</t>
+  </si>
+  <si>
+    <t>Schizophrene Psychosen</t>
+  </si>
+  <si>
+    <t>HDG20.10</t>
+  </si>
+  <si>
+    <t>Affektive Psychosen</t>
+  </si>
+  <si>
+    <t>HDG20.11</t>
+  </si>
+  <si>
+    <t>Psychosen des Kindesalters</t>
+  </si>
+  <si>
+    <t>HDG20.12</t>
+  </si>
+  <si>
+    <t>Neurosen/Persönlichkeitsstörungen/Eßstörungen</t>
+  </si>
+  <si>
+    <t>HDG20.13</t>
+  </si>
+  <si>
+    <t>Alkoholismus</t>
+  </si>
+  <si>
+    <t>HDG20.14</t>
+  </si>
+  <si>
+    <t>Medikamenten-, Drogenabhängigkeit</t>
+  </si>
+  <si>
+    <t>HDG20.15</t>
+  </si>
+  <si>
+    <t>Funktionelle Störungen psychischen Ursprungs</t>
+  </si>
+  <si>
+    <t>HDG20.16</t>
+  </si>
+  <si>
+    <t>Spezielle emotionale Störungen des Kindes- und Jugendalters</t>
+  </si>
+  <si>
+    <t>HDG20.17</t>
+  </si>
+  <si>
+    <t>Oligophrenien</t>
+  </si>
+  <si>
+    <t>HDG21.01</t>
+  </si>
+  <si>
+    <t>Vergiftungen</t>
+  </si>
+  <si>
+    <t>HDG21.03</t>
+  </si>
+  <si>
+    <t>Toxische Wirkungen exogener Noxen</t>
+  </si>
+  <si>
+    <t>HDG22.01</t>
+  </si>
+  <si>
+    <t>Schwerwiegende akute Zustände und Komplikationen</t>
+  </si>
+  <si>
+    <t>HDG22.03</t>
+  </si>
+  <si>
+    <t>Tod und Todesursachen</t>
+  </si>
+  <si>
+    <t>HDG22.04</t>
+  </si>
+  <si>
+    <t>Komplikationen nach Verletzungen und chirurgischen Eingriffen</t>
+  </si>
+  <si>
+    <t>HDG22.05</t>
+  </si>
+  <si>
+    <t>Schädigungen durch äußere Einflüsse</t>
+  </si>
+  <si>
+    <t>HDG23.02</t>
+  </si>
+  <si>
+    <t>Verdacht auf Neoplasie</t>
+  </si>
+  <si>
+    <t>HDG23.03</t>
+  </si>
+  <si>
+    <t>Andere Faktoren zur Inanspruchnahme des Gesundheitswesens</t>
+  </si>
+  <si>
+    <t>HDG24.01</t>
+  </si>
+  <si>
+    <t>Chromosomenanomalien</t>
+  </si>
+  <si>
+    <t>HDG24.02</t>
+  </si>
+  <si>
+    <t>Andere kongenitale Anomalien</t>
+  </si>
+  <si>
+    <t>HDG24.03</t>
+  </si>
+  <si>
+    <t>Sonstige unspezifische Befunde</t>
+  </si>
+  <si>
+    <t>MEL01.01</t>
+  </si>
+  <si>
+    <t>Eingriffe an der Schädeldecke</t>
+  </si>
+  <si>
+    <t>MEL01.02</t>
+  </si>
+  <si>
+    <t>Eingriffe am Gehirnschädel und oberflächliche intrakranielle Eingriffe, stereotaktische Eingriffe</t>
+  </si>
+  <si>
+    <t>MEL01.03</t>
+  </si>
+  <si>
+    <t>Tiefe intrakranielle Eingriffe I</t>
+  </si>
+  <si>
+    <t>MEL01.04</t>
+  </si>
+  <si>
+    <t>Tiefe intrakranielle Eingriffe II</t>
+  </si>
+  <si>
+    <t>MEL01.06</t>
+  </si>
+  <si>
+    <t>Laminektomien und Bandscheiben-Eingriffe / Eingriffe bei Sakralteratom</t>
+  </si>
+  <si>
+    <t>MEL01.07</t>
+  </si>
+  <si>
+    <t>Eingriffe am Rückenmark und seinen Hüllen</t>
+  </si>
+  <si>
+    <t>MEL01.08</t>
+  </si>
+  <si>
+    <t>Funktionelle Eingriffe an Rückenmark, Nerven und vegetativem Nervensystem / Implantation von Pumpensystemen</t>
+  </si>
+  <si>
+    <t>MEL01.09</t>
+  </si>
+  <si>
+    <t>Eingriffe zur Stabilisierung der Wirbelsäule I</t>
+  </si>
+  <si>
+    <t>MEL01.10</t>
+  </si>
+  <si>
+    <t>Eingriffe zur Stabilisierung der Wirbelsäule II</t>
+  </si>
+  <si>
+    <t>MEL01.11</t>
+  </si>
+  <si>
+    <t>Zervikale Bandscheiben-Operation</t>
+  </si>
+  <si>
+    <t>MEL01.12</t>
+  </si>
+  <si>
+    <t>Implantation von Elektroden zur Epilepsiediagnostik</t>
+  </si>
+  <si>
+    <t>MEL01.13</t>
+  </si>
+  <si>
+    <t>Implantation von Elektroden zur Hinterstrangstimulation und Stimulation peripherer Nerven</t>
+  </si>
+  <si>
+    <t>MEL01.14</t>
+  </si>
+  <si>
+    <t>Implantation von Elektroden zur Tiefenhirnstimulation</t>
+  </si>
+  <si>
+    <t>MEL01.15</t>
+  </si>
+  <si>
+    <t>Implantation eines Impulsgenerators am Nervensystem</t>
+  </si>
+  <si>
+    <t>MEL01.16</t>
+  </si>
+  <si>
+    <t>Implantation eines Systems zur N. Vagusstimulation</t>
+  </si>
+  <si>
+    <t>MEL01.17</t>
+  </si>
+  <si>
+    <t>Minimal-invasive Eingriffe im Bereich der Wirbelsäule</t>
+  </si>
+  <si>
+    <t>MEL01.18</t>
+  </si>
+  <si>
+    <t>Komplexe Eingriffe an der Wirbelsäule</t>
+  </si>
+  <si>
+    <t>MEL01.19</t>
+  </si>
+  <si>
+    <t>Teilimplantation eines Impulsgenerators</t>
+  </si>
+  <si>
+    <t>MEL01.20</t>
+  </si>
+  <si>
+    <t>Transkranielle Eingriffe</t>
+  </si>
+  <si>
+    <t>MEL02.01</t>
+  </si>
+  <si>
+    <t>Eingriffe an den peripheren Nerven</t>
+  </si>
+  <si>
+    <t>MEL02.02</t>
+  </si>
+  <si>
+    <t>Funktionell-plastische Eingriffe mit Beteiligung der peripheren Nerven</t>
+  </si>
+  <si>
+    <t>MEL02.03</t>
+  </si>
+  <si>
+    <t>Kleine Eingriffe an Bindegewebe, Haut und Weichteilen</t>
+  </si>
+  <si>
+    <t>MEL02.04</t>
+  </si>
+  <si>
+    <t>Plexuseingriffe</t>
+  </si>
+  <si>
+    <t>MEL03.01</t>
+  </si>
+  <si>
+    <t>Osteotomie, Resektion und Osteosynthese am Gesichtsschädel und Kiefer</t>
+  </si>
+  <si>
+    <t>MEL03.02</t>
+  </si>
+  <si>
+    <t>Rekonstruktive Eingriffe an Gesicht, Lippen und Mundhöhle</t>
+  </si>
+  <si>
+    <t>MEL03.03</t>
+  </si>
+  <si>
+    <t>Eingriff zur Korrektur von Deformitäten an Ober- und Unterkiefer</t>
+  </si>
+  <si>
+    <t>MEL03.04</t>
+  </si>
+  <si>
+    <t>Eingriffe zur Korrektur kraniofazialer Deformitäten</t>
+  </si>
+  <si>
+    <t>MEL04.01</t>
+  </si>
+  <si>
+    <t>Eingriffe am äußeren Ohr und Mittelohr, Eingriffe zur Versorgung einer Liquorrhoe</t>
+  </si>
+  <si>
+    <t>MEL04.02</t>
+  </si>
+  <si>
+    <t>Eingriffe am intrakraniellen Innenohr</t>
+  </si>
+  <si>
+    <t>MEL04.03</t>
+  </si>
+  <si>
+    <t>Eingriffe an der Nase und Nasennebenhöhlen</t>
+  </si>
+  <si>
+    <t>MEL04.04</t>
+  </si>
+  <si>
+    <t>Tonsillektomie, Adenotomie, Paracentese</t>
+  </si>
+  <si>
+    <t>MEL04.05</t>
+  </si>
+  <si>
+    <t>Mikrochirurgische und endoskopische Eingriffe an den Nasennebenhöhlen</t>
+  </si>
+  <si>
+    <t>MEL04.06</t>
+  </si>
+  <si>
+    <t>Eingriffe an den Speicheldrüsen</t>
+  </si>
+  <si>
+    <t>MEL04.07</t>
+  </si>
+  <si>
+    <t>Komplexe Eingriffe am Hals und den oberen Atemwegen</t>
+  </si>
+  <si>
+    <t>MEL04.08</t>
+  </si>
+  <si>
+    <t>Eingriffe an den oberen Atemwegen</t>
+  </si>
+  <si>
+    <t>MEL04.09</t>
+  </si>
+  <si>
+    <t>Cochlearimplantat und elektronisches Mittelohrimplantat</t>
+  </si>
+  <si>
+    <t>MEL04.10</t>
+  </si>
+  <si>
+    <t>Eingriffe an der Schilddrüse und Nebenschilddrüse</t>
+  </si>
+  <si>
+    <t>MEL05.01</t>
+  </si>
+  <si>
+    <t>Eingriffe am Ösophagus, Magen und Zwerchfell</t>
+  </si>
+  <si>
+    <t>MEL05.02</t>
+  </si>
+  <si>
+    <t>Ösophagusresektion</t>
+  </si>
+  <si>
+    <t>MEL05.03</t>
+  </si>
+  <si>
+    <t>Magenteilresektion</t>
+  </si>
+  <si>
+    <t>MEL05.04</t>
+  </si>
+  <si>
+    <t>Totale und subtotale Gastrektomie</t>
+  </si>
+  <si>
+    <t>MEL05.05</t>
+  </si>
+  <si>
+    <t>Cholezystektomie</t>
+  </si>
+  <si>
+    <t>MEL05.06</t>
+  </si>
+  <si>
+    <t>Eingriffe am Gallengangsystem</t>
+  </si>
+  <si>
+    <t>MEL05.07</t>
+  </si>
+  <si>
+    <t>Eingriffe an Milz, Leber, Duodenum und Pankreas</t>
+  </si>
+  <si>
+    <t>MEL05.08</t>
+  </si>
+  <si>
+    <t>Eingriffe am Pankreas</t>
+  </si>
+  <si>
+    <t>MEL06.01</t>
+  </si>
+  <si>
+    <t>Appendektomie</t>
+  </si>
+  <si>
+    <t>MEL06.02</t>
+  </si>
+  <si>
+    <t>Eingriffe an Dünndarm und Dickdarm</t>
+  </si>
+  <si>
+    <t>MEL06.03</t>
+  </si>
+  <si>
+    <t>Eingriffe an Dickdarm und Rektum</t>
+  </si>
+  <si>
+    <t>MEL06.04</t>
+  </si>
+  <si>
+    <t>Komplexe Eingriffe an Dickdarm und Rektum</t>
+  </si>
+  <si>
+    <t>MEL06.05</t>
+  </si>
+  <si>
+    <t>Eingriffe an der Bauchwand, Laparotomie</t>
+  </si>
+  <si>
+    <t>MEL06.06</t>
+  </si>
+  <si>
+    <t>Eingriffe bei Bauchwandhernien, Leistenhernien beim Kind</t>
+  </si>
+  <si>
+    <t>MEL06.08</t>
+  </si>
+  <si>
+    <t>Komplexe Eingriffe an Rektum und Anus</t>
+  </si>
+  <si>
+    <t>MEL06.09</t>
+  </si>
+  <si>
+    <t>Eingriffe an Rektum und Anus</t>
+  </si>
+  <si>
+    <t>MEL06.11</t>
+  </si>
+  <si>
+    <t>Laparoskopie diagnostisch/therapeutisch</t>
+  </si>
+  <si>
+    <t>MEL07.01</t>
+  </si>
+  <si>
+    <t>Anatomische Lungenresektion</t>
+  </si>
+  <si>
+    <t>MEL07.02</t>
+  </si>
+  <si>
+    <t>Einfache thoraxchirurgische Eingriffe</t>
+  </si>
+  <si>
+    <t>MEL07.03</t>
+  </si>
+  <si>
+    <t>Erweiterte anatomische Lungenresektionen</t>
+  </si>
+  <si>
+    <t>MEL07.04</t>
+  </si>
+  <si>
+    <t>Eingriffe an der Thoraxwand</t>
+  </si>
+  <si>
+    <t>MEL07.05</t>
+  </si>
+  <si>
+    <t>Implantation eines Zwerchfell-Schrittmachers</t>
+  </si>
+  <si>
+    <t>MEL07.06</t>
+  </si>
+  <si>
+    <t>Bronchoskopische Lungenvolumenreduktion</t>
+  </si>
+  <si>
+    <t>MEL08.01</t>
+  </si>
+  <si>
+    <t>Eingriffe am Herzen ohne Herz-Lungen-Maschine</t>
+  </si>
+  <si>
+    <t>MEL08.02</t>
+  </si>
+  <si>
+    <t>Koronare Revaskularisation und andere Eingriffe am Herzen mit HLM</t>
+  </si>
+  <si>
+    <t>MEL08.03</t>
+  </si>
+  <si>
+    <t>Eingriffe an den Herzklappen und Aorta ascendens mit HLM</t>
+  </si>
+  <si>
+    <t>MEL08.05</t>
+  </si>
+  <si>
+    <t>Rekonstruktion der Aorta ascendens und des Aortenbogens mit Kreislaufstillstand, Korrektur komplexer Herzfehler</t>
+  </si>
+  <si>
+    <t>MEL08.06</t>
+  </si>
+  <si>
+    <t>Ventrikelersatz</t>
+  </si>
+  <si>
+    <t>MEL08.07</t>
+  </si>
+  <si>
+    <t>Rekonstruktionen an der thorakalen-thorakoabdominellen Aorta</t>
+  </si>
+  <si>
+    <t>MEL08.08</t>
+  </si>
+  <si>
+    <t>Thorakoskopische Eingriffe</t>
+  </si>
+  <si>
+    <t>MEL08.09</t>
+  </si>
+  <si>
+    <t>Implantation eines Aortenstents</t>
+  </si>
+  <si>
+    <t>MEL08.10</t>
+  </si>
+  <si>
+    <t>Implantation eines Systems zur extrakorporalen Membranoxygenierung (ECMO)</t>
+  </si>
+  <si>
+    <t>MEL08.11</t>
+  </si>
+  <si>
+    <t>Implantation eines herzunterstützenden Systems</t>
+  </si>
+  <si>
+    <t>MEL09.01</t>
+  </si>
+  <si>
+    <t>Rekonstruktionen an den peripheren Gefäßen</t>
+  </si>
+  <si>
+    <t>MEL09.02</t>
+  </si>
+  <si>
+    <t>Rekonstruktionen an der abdominellen Aorta und den viszeralen Gefäßen</t>
+  </si>
+  <si>
+    <t>MEL09.03</t>
+  </si>
+  <si>
+    <t>Eingriffe an den peripheren Gefäßen</t>
+  </si>
+  <si>
+    <t>MEL09.04</t>
+  </si>
+  <si>
+    <t>Isolierte Organperfusion</t>
+  </si>
+  <si>
+    <t>MEL09.05</t>
+  </si>
+  <si>
+    <t>Implantation eines Loop-Recorders</t>
+  </si>
+  <si>
+    <t>MEL10.01</t>
+  </si>
+  <si>
+    <t>Implantation eines Schrittmachers</t>
+  </si>
+  <si>
+    <t>MEL10.02</t>
+  </si>
+  <si>
+    <t>Implantation eines Defibrillators</t>
+  </si>
+  <si>
+    <t>MEL10.03</t>
+  </si>
+  <si>
+    <t>Implantation von Systemen zur kardialen Resynchronisation</t>
+  </si>
+  <si>
+    <t>MEL10.04</t>
+  </si>
+  <si>
+    <t>Implantation eines automatischen Kardioverters -Defibrillators mit kardialer Resynchronisationsfunktion</t>
+  </si>
+  <si>
+    <t>MEL10.05</t>
+  </si>
+  <si>
+    <t>Extraktion von Schrittmachersonden</t>
+  </si>
+  <si>
+    <t>MEL11.01</t>
+  </si>
+  <si>
+    <t>Eingriffe an Niere und Harnleiter I</t>
+  </si>
+  <si>
+    <t>MEL11.02</t>
+  </si>
+  <si>
+    <t>Komplexe Eingriffe an der Harnblase</t>
+  </si>
+  <si>
+    <t>MEL11.03</t>
+  </si>
+  <si>
+    <t>Eingriffe an Niere und Harnleiter II</t>
+  </si>
+  <si>
+    <t>MEL11.04</t>
+  </si>
+  <si>
+    <t>Eingriffe an Niere und Harnleiter III</t>
+  </si>
+  <si>
+    <t>MEL11.05</t>
+  </si>
+  <si>
+    <t>Eingriffe an Harnblase und Urethra</t>
+  </si>
+  <si>
+    <t>MEL11.06</t>
+  </si>
+  <si>
+    <t>Funktionseingriffe an Harnblase und Urethra</t>
+  </si>
+  <si>
+    <t>MEL11.07</t>
+  </si>
+  <si>
+    <t>Transurethrale Resektion der Harnblase</t>
+  </si>
+  <si>
+    <t>MEL12.01</t>
+  </si>
+  <si>
+    <t>Prostatektomie</t>
+  </si>
+  <si>
+    <t>MEL12.02</t>
+  </si>
+  <si>
+    <t>Implantation Penisprothese</t>
+  </si>
+  <si>
+    <t>MEL12.03</t>
+  </si>
+  <si>
+    <t>Transurethrale Resektion der Prostata</t>
+  </si>
+  <si>
+    <t>MEL12.04</t>
+  </si>
+  <si>
+    <t>Eingriffe am äußeren männlichen Genitale</t>
+  </si>
+  <si>
+    <t>MEL12.05</t>
+  </si>
+  <si>
+    <t>Einfache Eingriffe am äußeren männlichen Genitale</t>
+  </si>
+  <si>
+    <t>MEL13.01</t>
+  </si>
+  <si>
+    <t>Komplexe Hysterektomien</t>
+  </si>
+  <si>
+    <t>MEL13.02</t>
+  </si>
+  <si>
+    <t>Eingriffe am Uterus</t>
+  </si>
+  <si>
+    <t>MEL13.03</t>
+  </si>
+  <si>
+    <t>Laparoskopische Eingriffe an den weiblichen Beckenorganen</t>
+  </si>
+  <si>
+    <t>MEL13.04</t>
+  </si>
+  <si>
+    <t>Eingriffe an den weiblichen Beckenorganen und Beckenboden I</t>
+  </si>
+  <si>
+    <t>MEL13.05</t>
+  </si>
+  <si>
+    <t>Eingriffe an den weiblichen Beckenorganen und Beckenboden II</t>
+  </si>
+  <si>
+    <t>MEL13.06</t>
+  </si>
+  <si>
+    <t>Hysterektomien</t>
+  </si>
+  <si>
+    <t>MEL13.07</t>
+  </si>
+  <si>
+    <t>Einfache Eingriffe am Uterus</t>
+  </si>
+  <si>
+    <t>MEL13.09</t>
+  </si>
+  <si>
+    <t>Entbindung</t>
+  </si>
+  <si>
+    <t>MEL13.10</t>
+  </si>
+  <si>
+    <t>Eingriffe an den Adnexen</t>
+  </si>
+  <si>
+    <t>MEL13.13</t>
+  </si>
+  <si>
+    <t>Fetoskopische Eingriffe</t>
+  </si>
+  <si>
+    <t>MEL14.01</t>
+  </si>
+  <si>
+    <t>Osteosynthesen und Osteotomien an Schulter, Oberarm und Ellbogen</t>
+  </si>
+  <si>
+    <t>MEL14.02</t>
+  </si>
+  <si>
+    <t>Eingriffe an Schulter, Oberarm und Ellbogen</t>
+  </si>
+  <si>
+    <t>MEL14.03</t>
+  </si>
+  <si>
+    <t>Eingriffe an Unterarm, Handwurzel und Hand</t>
+  </si>
+  <si>
+    <t>MEL14.04</t>
+  </si>
+  <si>
+    <t>Endoprothetik des Schultergelenks</t>
+  </si>
+  <si>
+    <t>MEL14.05</t>
+  </si>
+  <si>
+    <t>Endoprothetik des Ellbogengelenks</t>
+  </si>
+  <si>
+    <t>MEL14.06</t>
+  </si>
+  <si>
+    <t>Endoprothetik der Hand</t>
+  </si>
+  <si>
+    <t>MEL14.07</t>
+  </si>
+  <si>
+    <t>Teilendoprothetik des Hüftgelenks</t>
+  </si>
+  <si>
+    <t>MEL14.08</t>
+  </si>
+  <si>
+    <t>Totalendoprothetik des Hüftgelenks</t>
+  </si>
+  <si>
+    <t>MEL14.09</t>
+  </si>
+  <si>
+    <t>Teilendoprothetik des Kniegelenks</t>
+  </si>
+  <si>
+    <t>MEL14.10</t>
+  </si>
+  <si>
+    <t>Totalendoprothetik des Kniegelenks</t>
+  </si>
+  <si>
+    <t>MEL14.11</t>
+  </si>
+  <si>
+    <t>Endoprothetik des Sprunggelenks</t>
+  </si>
+  <si>
+    <t>MEL14.12</t>
+  </si>
+  <si>
+    <t>Wechsel von Prothesenteilen</t>
+  </si>
+  <si>
+    <t>MEL14.13</t>
+  </si>
+  <si>
+    <t>Komplexe Eingriffe an Knie und Unterschenkel</t>
+  </si>
+  <si>
+    <t>MEL14.14</t>
+  </si>
+  <si>
+    <t>Eingriffe an Knie und Unterschenkel</t>
+  </si>
+  <si>
+    <t>MEL14.15</t>
+  </si>
+  <si>
+    <t>Eingriffe an Fuß, Mittelfuß und Zehen</t>
+  </si>
+  <si>
+    <t>MEL14.16</t>
+  </si>
+  <si>
+    <t>Amputationen</t>
+  </si>
+  <si>
+    <t>MEL14.17</t>
+  </si>
+  <si>
+    <t>Komplexe Eingriffe am Beckenring</t>
+  </si>
+  <si>
+    <t>MEL14.18</t>
+  </si>
+  <si>
+    <t>Eingriffe an Hüfte und Oberschenkel</t>
+  </si>
+  <si>
+    <t>MEL14.19</t>
+  </si>
+  <si>
+    <t>Replantationseingriffe</t>
+  </si>
+  <si>
+    <t>MEL14.21</t>
+  </si>
+  <si>
+    <t>Arthroskopische Eingriffe</t>
+  </si>
+  <si>
+    <t>MEL14.22</t>
+  </si>
+  <si>
+    <t>Eingriffe an Bewegungsapparat und Haut</t>
+  </si>
+  <si>
+    <t>MEL14.23</t>
+  </si>
+  <si>
+    <t>Entfernung von Osteosynthesematerial</t>
+  </si>
+  <si>
+    <t>MEL14.24</t>
+  </si>
+  <si>
+    <t>Komplexe plastische Eingriffe an der Haut/ Lappenchirurgie</t>
+  </si>
+  <si>
+    <t>MEL14.25</t>
+  </si>
+  <si>
+    <t>Komplexe orthopädische Eingriffe</t>
+  </si>
+  <si>
+    <t>MEL14.26</t>
+  </si>
+  <si>
+    <t>Implantation von Spezialprothesen</t>
+  </si>
+  <si>
+    <t>MEL14.27</t>
+  </si>
+  <si>
+    <t>Endoprothetik Mittelfuß und Zehen</t>
+  </si>
+  <si>
+    <t>MEL14.28</t>
+  </si>
+  <si>
+    <t>Endoprothetik des Kiefergelenks</t>
+  </si>
+  <si>
+    <t>MEL15.01</t>
+  </si>
+  <si>
+    <t>Plastische Eingriffe am äußeren Auge</t>
+  </si>
+  <si>
+    <t>MEL15.02</t>
+  </si>
+  <si>
+    <t>Eingriffe an der Orbita und am Bulbus</t>
+  </si>
+  <si>
+    <t>MEL15.03</t>
+  </si>
+  <si>
+    <t>Schiel-Operationen</t>
+  </si>
+  <si>
+    <t>MEL15.04</t>
+  </si>
+  <si>
+    <t>Glaukom-Operationen</t>
+  </si>
+  <si>
+    <t>MEL15.05</t>
+  </si>
+  <si>
+    <t>Katarakt-Operationen</t>
+  </si>
+  <si>
+    <t>MEL15.06</t>
+  </si>
+  <si>
+    <t>Eingriffe an der Hornhaut</t>
+  </si>
+  <si>
+    <t>MEL15.07</t>
+  </si>
+  <si>
+    <t>Eingriffe an der Netzhaut und am Glaskörper</t>
+  </si>
+  <si>
+    <t>MEL16.01</t>
+  </si>
+  <si>
+    <t>Resektionen an der Mamma</t>
+  </si>
+  <si>
+    <t>MEL16.02</t>
+  </si>
+  <si>
+    <t>Plastische Eingriffe an der Mamma</t>
+  </si>
+  <si>
+    <t>MEL17.01</t>
+  </si>
+  <si>
+    <t>Lymphadenektomien</t>
+  </si>
+  <si>
+    <t>MEL17.02</t>
+  </si>
+  <si>
+    <t>Komplexe Lymphoadenektomien, Entfernung retroperitonealer Raumforderungen</t>
+  </si>
+  <si>
+    <t>MEL17.03</t>
+  </si>
+  <si>
+    <t>Rekonstruktive Eingriffe am Lymphsystem</t>
+  </si>
+  <si>
+    <t>MEL18.02</t>
+  </si>
+  <si>
+    <t>Implantation der Niere</t>
+  </si>
+  <si>
+    <t>MEL18.03</t>
+  </si>
+  <si>
+    <t>Implantation von Leber/Dünndarm</t>
+  </si>
+  <si>
+    <t>MEL18.04</t>
+  </si>
+  <si>
+    <t>Implantation des Pankreas</t>
+  </si>
+  <si>
+    <t>MEL18.05</t>
+  </si>
+  <si>
+    <t>Implantation des Herzens</t>
+  </si>
+  <si>
+    <t>MEL18.06</t>
+  </si>
+  <si>
+    <t>Implantation der Lunge</t>
+  </si>
+  <si>
+    <t>MEL18.07</t>
+  </si>
+  <si>
+    <t>Implantation von Herz und Lunge</t>
+  </si>
+  <si>
+    <t>MEL19.01</t>
+  </si>
+  <si>
+    <t>Radiochirurgie mit Gammastrahlen</t>
+  </si>
+  <si>
+    <t>MEL20.01</t>
+  </si>
+  <si>
+    <t>Interventionelle Radiologie an den Gefäßen</t>
+  </si>
+  <si>
+    <t>MEL20.02</t>
+  </si>
+  <si>
+    <t>Radiofrequenztherapie</t>
+  </si>
+  <si>
+    <t>MEL21.01</t>
+  </si>
+  <si>
+    <t>Interventionelle Kardiologie - Koronarangiografie</t>
+  </si>
+  <si>
+    <t>MEL21.03</t>
+  </si>
+  <si>
+    <t>Interventionelle Kardiologie - Alternative Revaskularisationsverfahren</t>
+  </si>
+  <si>
+    <t>MEL21.04</t>
+  </si>
+  <si>
+    <t>Interventionelle Kardiologie - Rhythmologie</t>
+  </si>
+  <si>
+    <t>MEL21.05</t>
+  </si>
+  <si>
+    <t>Interventionelle Kardiologie - Vitientherapie</t>
+  </si>
+  <si>
+    <t>MEL21.08</t>
+  </si>
+  <si>
+    <t>Interventionelle Kardiologie - Thrombusaspiration</t>
+  </si>
+  <si>
+    <t>MEL21.10</t>
+  </si>
+  <si>
+    <t>Interventionelle Kardiologie - Distale Protektion</t>
+  </si>
+  <si>
+    <t>MEL21.11</t>
+  </si>
+  <si>
+    <t>Interventionelle Kardiologie - Revaskularisation</t>
+  </si>
+  <si>
+    <t>MEL22.01</t>
+  </si>
+  <si>
+    <t>Chemotherapie bei malignen Erkrankungen d. Leistungsgruppe A</t>
+  </si>
+  <si>
+    <t>MEL22.02</t>
+  </si>
+  <si>
+    <t>Chemotherapie bei malignen Erkrankungen d. Leistungsgruppe B</t>
+  </si>
+  <si>
+    <t>MEL22.03</t>
+  </si>
+  <si>
+    <t>Chemotherapie bei malignen Erkrankungen d. Leistungsgruppe C</t>
+  </si>
+  <si>
+    <t>MEL22.04</t>
+  </si>
+  <si>
+    <t>Chemotherapie bei malignen Erkrankungen d. Leistungsgruppe D</t>
+  </si>
+  <si>
+    <t>MEL22.05</t>
+  </si>
+  <si>
+    <t>Chemotherapie bei malignen Erkrankungen d. Leistungsgruppe E</t>
+  </si>
+  <si>
+    <t>MEL22.06</t>
+  </si>
+  <si>
+    <t>Chemotherapie bei malignen Erkrankungen d. Leistungsgruppe F</t>
+  </si>
+  <si>
+    <t>MEL22.08</t>
+  </si>
+  <si>
+    <t>Allogene Stammzelltransplantation - verwandte Spender</t>
+  </si>
+  <si>
+    <t>MEL22.09</t>
+  </si>
+  <si>
+    <t>Allogene Stammzelltransplantation - unverwandte Spender</t>
+  </si>
+  <si>
+    <t>MEL22.10</t>
+  </si>
+  <si>
+    <t>Autologe Stammzelltransplantation</t>
+  </si>
+  <si>
+    <t>MEL22.11</t>
+  </si>
+  <si>
+    <t>Gewinnung von Stammzellen aus Knochenmark/Blut - ohne Purging</t>
+  </si>
+  <si>
+    <t>MEL22.13</t>
+  </si>
+  <si>
+    <t>Andere, zusätzliche oder begleitende onkologische Therapie - Zytokine</t>
+  </si>
+  <si>
+    <t>MEL22.14</t>
+  </si>
+  <si>
+    <t>Andere, zusätzliche oder begleitende onkologische Therapie - monoklonale Antikörper</t>
+  </si>
+  <si>
+    <t>MEL22.16</t>
+  </si>
+  <si>
+    <t>Fortsetzung einer Chemotherapie oder Verabreichen nicht kostenrelevanter Zytostatika</t>
+  </si>
+  <si>
+    <t>MEL22.18</t>
+  </si>
+  <si>
+    <t>Zellseperator-Thrombozytenkonzentrat von Einzelspendern</t>
+  </si>
+  <si>
+    <t>MEL22.19</t>
+  </si>
+  <si>
+    <t>Spezifische Gammaglobulin-Verabreichung nach Stammzelltransplantation</t>
+  </si>
+  <si>
+    <t>MEL22.20</t>
+  </si>
+  <si>
+    <t>Gabe von Einzelfaktorkonzentraten bei angeborenen Gerinnungsstörungen und Hemmkörperhämophilie</t>
+  </si>
+  <si>
+    <t>MEL22.21</t>
+  </si>
+  <si>
+    <t>Graft versus Host Erkrankung (GvHD)</t>
+  </si>
+  <si>
+    <t>MEL22.22</t>
+  </si>
+  <si>
+    <t>Andere spezifische Tumortherapie</t>
+  </si>
+  <si>
+    <t>MEL22.23</t>
+  </si>
+  <si>
+    <t>Radioaktiv markierte Antikörper</t>
+  </si>
+  <si>
+    <t>MEL22.24</t>
+  </si>
+  <si>
+    <t>Verabreichung von Spenderlymphozyten nach allogener Stammzelltransplantation</t>
+  </si>
+  <si>
+    <t>MEL22.26</t>
+  </si>
+  <si>
+    <t>Andere, zusätzliche oder begleitende onkologische Therapien - Sonstige</t>
+  </si>
+  <si>
+    <t>MEL22.27</t>
+  </si>
+  <si>
+    <t>Onkologische Immuntherapie</t>
+  </si>
+  <si>
+    <t>MEL22.28</t>
+  </si>
+  <si>
+    <t>Pädiatrische onkologische Therapie - Basistherapie</t>
+  </si>
+  <si>
+    <t>MEL22.29</t>
+  </si>
+  <si>
+    <t>Pädiatrische onkologische Therapie - spezielle Therapie</t>
+  </si>
+  <si>
+    <t>MEL22.30</t>
+  </si>
+  <si>
+    <t>Verabreichung von modifizierten Zellen</t>
+  </si>
+  <si>
+    <t>MEL22.31</t>
+  </si>
+  <si>
+    <t>Lokoregionale Hyperthermie</t>
+  </si>
+  <si>
+    <t>MEL23.01</t>
+  </si>
+  <si>
+    <t>Alkoholentwöhnung im Turnus 6 bis 12 Wochen</t>
+  </si>
+  <si>
+    <t>MEL23.02</t>
+  </si>
+  <si>
+    <t>Drogenentwöhnungen auf Drogenstationen</t>
+  </si>
+  <si>
+    <t>MEL24.01</t>
+  </si>
+  <si>
+    <t>Nierenersatztherapie</t>
+  </si>
+  <si>
+    <t>MEL24.02</t>
+  </si>
+  <si>
+    <t>Plasmapherese, Plasmafiltration</t>
+  </si>
+  <si>
+    <t>MEL24.03</t>
+  </si>
+  <si>
+    <t>Adsorptionssystem und Dialyse albumingebundener Substanzen</t>
+  </si>
+  <si>
+    <t>MEL24.04</t>
+  </si>
+  <si>
+    <t>Photopherese</t>
+  </si>
+  <si>
+    <t>MEL25.02</t>
+  </si>
+  <si>
+    <t>Brachytherapie</t>
+  </si>
+  <si>
+    <t>MEL25.04</t>
+  </si>
+  <si>
+    <t>Radionuklidtherapie I</t>
+  </si>
+  <si>
+    <t>MEL25.05</t>
+  </si>
+  <si>
+    <t>Radionuklidtherapie II</t>
+  </si>
+  <si>
+    <t>MEL25.06</t>
+  </si>
+  <si>
+    <t>Implantation von radioaktiven Prostataseeds</t>
+  </si>
+  <si>
+    <t>MEL25.07</t>
+  </si>
+  <si>
+    <t>Intraoperative Radiotherapie</t>
+  </si>
+  <si>
+    <t>MEL25.08</t>
+  </si>
+  <si>
+    <t>Konventionelle Teletherapie</t>
+  </si>
+  <si>
+    <t>MEL25.09</t>
+  </si>
+  <si>
+    <t>Intensitätsmodulierte Teletherapie und stereotaktische Radiochirurgie</t>
+  </si>
+  <si>
+    <t>MEL25.10</t>
+  </si>
+  <si>
+    <t>Ergänzende Verfahren in der Strahlentherapie</t>
+  </si>
+  <si>
+    <t>MEL26.01</t>
+  </si>
+  <si>
+    <t>Systemische Lysetherapie</t>
+  </si>
+  <si>
+    <t>MEL26.02</t>
+  </si>
+  <si>
+    <t>Akute Insulttherapie auf Schlaganfalleinheiten (stroke unit)</t>
+  </si>
+  <si>
+    <t>MEL27.01</t>
+  </si>
+  <si>
+    <t>Hyperbare Oxygenation</t>
+  </si>
+  <si>
+    <t>MEL29.01</t>
+  </si>
+  <si>
+    <t>Extrakorporale/endoskopische Steinbehandlung</t>
+  </si>
+  <si>
+    <t>MEL29.02</t>
+  </si>
+  <si>
+    <t>Therapeutische ERCP / endoskopische Prothesenimplantation</t>
+  </si>
+  <si>
+    <t>MEL30.01</t>
+  </si>
+  <si>
+    <t>AIDS-Behandlung</t>
+  </si>
+  <si>
+    <t>MEL32.01</t>
+  </si>
+  <si>
+    <t>Behandlung in der PSO im Turnus (Erwachsene)</t>
+  </si>
+  <si>
+    <t>MEL32.03</t>
+  </si>
+  <si>
+    <t>Behandlung in der PSO im Turnus (Kinder und Jugendliche)</t>
   </si>
   <si>
     <t>DIAG0PKT</t>
@@ -431,7 +2981,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B439"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -536,18 +3086,3418 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B231" t="s" s="2">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B243" t="s" s="2">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B256" t="s" s="2">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B265" t="s" s="2">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B274" t="s" s="2">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B275" t="s" s="2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B276" t="s" s="2">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B278" t="s" s="2">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B279" t="s" s="2">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B280" t="s" s="2">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B281" t="s" s="2">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B286" t="s" s="2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B287" t="s" s="2">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B288" t="s" s="2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B289" t="s" s="2">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B290" t="s" s="2">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B292" t="s" s="2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B293" t="s" s="2">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B294" t="s" s="2">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B295" t="s" s="2">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B296" t="s" s="2">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B297" t="s" s="2">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B298" t="s" s="2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B300" t="s" s="2">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B301" t="s" s="2">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B302" t="s" s="2">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B303" t="s" s="2">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B304" t="s" s="2">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B305" t="s" s="2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B306" t="s" s="2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B307" t="s" s="2">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B308" t="s" s="2">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B309" t="s" s="2">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B310" t="s" s="2">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B311" t="s" s="2">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B312" t="s" s="2">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B313" t="s" s="2">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B314" t="s" s="2">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B315" t="s" s="2">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B316" t="s" s="2">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B317" t="s" s="2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B318" t="s" s="2">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B319" t="s" s="2">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B320" t="s" s="2">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="B321" t="s" s="2">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B322" t="s" s="2">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B323" t="s" s="2">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B324" t="s" s="2">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B325" t="s" s="2">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B326" t="s" s="2">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B327" t="s" s="2">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="B328" t="s" s="2">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B329" t="s" s="2">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B330" t="s" s="2">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B331" t="s" s="2">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B332" t="s" s="2">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B333" t="s" s="2">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B334" t="s" s="2">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="B335" t="s" s="2">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B336" t="s" s="2">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="B337" t="s" s="2">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="B338" t="s" s="2">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B339" t="s" s="2">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="B340" t="s" s="2">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B341" t="s" s="2">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="B342" t="s" s="2">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="B343" t="s" s="2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B344" t="s" s="2">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B345" t="s" s="2">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="B346" t="s" s="2">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B347" t="s" s="2">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="B348" t="s" s="2">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="B349" t="s" s="2">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="B350" t="s" s="2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="B351" t="s" s="2">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="B352" t="s" s="2">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="B353" t="s" s="2">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="B354" t="s" s="2">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="B355" t="s" s="2">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="B356" t="s" s="2">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="B357" t="s" s="2">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="B358" t="s" s="2">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="B359" t="s" s="2">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="B360" t="s" s="2">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="B361" t="s" s="2">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B362" t="s" s="2">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B363" t="s" s="2">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="B364" t="s" s="2">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B365" t="s" s="2">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="B366" t="s" s="2">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B367" t="s" s="2">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B368" t="s" s="2">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="B369" t="s" s="2">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="B370" t="s" s="2">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B371" t="s" s="2">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B372" t="s" s="2">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B373" t="s" s="2">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="B374" t="s" s="2">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="B375" t="s" s="2">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="B376" t="s" s="2">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="B377" t="s" s="2">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="B378" t="s" s="2">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="B379" t="s" s="2">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="B380" t="s" s="2">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="B381" t="s" s="2">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="B382" t="s" s="2">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="B383" t="s" s="2">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="B384" t="s" s="2">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="B385" t="s" s="2">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="B386" t="s" s="2">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="B387" t="s" s="2">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="B388" t="s" s="2">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B389" t="s" s="2">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="B390" t="s" s="2">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="B391" t="s" s="2">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="B392" t="s" s="2">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="B393" t="s" s="2">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="B394" t="s" s="2">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="B395" t="s" s="2">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="B396" t="s" s="2">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="B397" t="s" s="2">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="B398" t="s" s="2">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="B399" t="s" s="2">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="B400" t="s" s="2">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="B401" t="s" s="2">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="B402" t="s" s="2">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="B403" t="s" s="2">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="B404" t="s" s="2">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="B405" t="s" s="2">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="B406" t="s" s="2">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="B407" t="s" s="2">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="B408" t="s" s="2">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="B409" t="s" s="2">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="B410" t="s" s="2">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="B411" t="s" s="2">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="B412" t="s" s="2">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="B413" t="s" s="2">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="B414" t="s" s="2">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="B415" t="s" s="2">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="B416" t="s" s="2">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="B417" t="s" s="2">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="B418" t="s" s="2">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="B419" t="s" s="2">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="B420" t="s" s="2">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="B421" t="s" s="2">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="B422" t="s" s="2">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="B423" t="s" s="2">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="B424" t="s" s="2">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="B425" t="s" s="2">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="B426" t="s" s="2">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="B427" t="s" s="2">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="B428" t="s" s="2">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="B429" t="s" s="2">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="B430" t="s" s="2">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="B431" t="s" s="2">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="B432" t="s" s="2">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="B433" t="s" s="2">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="B434" t="s" s="2">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="B435" t="s" s="2">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="B436" t="s" s="2">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="B437" t="s" s="2">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B438" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="B439" t="s" s="2">
+        <v>900</v>
       </c>
     </row>
   </sheetData>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-LKFAbrechnungsGruppe-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
